--- a/大分県_運送会社リスト.xlsx
+++ b/大分県_運送会社リスト.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G217"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,172 +456,124 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>中津運送有限会社</t>
+          <t>株式会社三勢</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>大分県中津市伊藤田3630−1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0979-32-8060</t>
-        </is>
-      </c>
+          <t>大分県中津市大字上如水1203番地</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>株式会社中津急行</t>
+          <t>周防灘運送有限会社</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>https://nakakyu.com/</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>大分県中津市大字田尻崎7番地1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0979-32-5555</t>
-        </is>
-      </c>
+          <t>大分県中津市大字下池永1032番地9</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>株式会社ジャパンライン</t>
+          <t>中津運送有限会社</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>大分県中津市大字福島740番地の2</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>大分県中津市大字伊藤田字平田3630-1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0979-32-8060</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>株式会社桜瀬運輸</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all.right@hi3.enjoy.ne.jp</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>https://all-right-dream.com/</t>
-        </is>
-      </c>
+          <t>有限会社東運輸</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>大分県中津市大字福島745番地の5</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0979-33-7807</t>
-        </is>
-      </c>
+          <t>大分県中津市大字大新田828-8</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://all-right-dream.com/#contact</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>引越革命九州株式会社</t>
+          <t>株式会社アイビーユー</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>https://www.2020.co.jp/kyusyu</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>大分県別府市古市町881−187</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0120-443-677</t>
-        </is>
-      </c>
+          <t>大分県中津市大字大貞383番地74</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>株式会社鶴見</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>info@tsurumi-logi.com</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>http://tsurumi-logi.com/</t>
-        </is>
-      </c>
+          <t>司商事有限会社</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>大分県別府市新別府町42−67−2</t>
+          <t>大分県中津市大字島田217番地の9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0977-67-1661</t>
+          <t>0974-27-4443</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>http://tsurumi-logi.com/information/inquiry/</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>株式会社鶴見運送</t>
+          <t>有限会社東浜陸運</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>https://tsurumi-logi.com/about/index.html#outline</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>大分県別府市新別府町42番14号</t>
+          <t>大分県中津市大字植野60-1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -631,68 +583,64 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>有限会社椎原急配</t>
+          <t>有限会社幸運</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>大分県大分市ひばりケ丘3丁目9番2号</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>097-597-1413</t>
-        </is>
-      </c>
+          <t>大分県中津市大字植野字平田69番1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>株式会社ジキシン</t>
+          <t>中津ダイキュー運輸株式会社</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jikishin@ae.auone-net.jp</t>
+          <t>n20@kurumeunsou.co.jp</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://jikishin.jp/</t>
+          <t>https://daikyu-kumiai.com/group-nakatsu/</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>大分県大分市三佐4丁目265番地</t>
+          <t>大分県中津市大字犬丸1685</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>097-589-8330</t>
+          <t>0979-32-2131</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://jikishin.jp/contact</t>
+          <t>https://daikyu-kumiai.com/contact/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>株式会社FIRST EXPRESS</t>
+          <t>トランスポート・エス株式会社</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>大分県大分市三川新町2丁目1番8号</t>
+          <t>大分県中津市大字犬丸字野田高山2157-1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -702,89 +650,89 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>トランステック九州有限会社</t>
+          <t>株式会社中津急行</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://nakakyu.com/</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>大分県大分市上戸次3681</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>大分県中津市大字田尻崎7-1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>097-592-5555</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>大分丸善運輸株式会社</t>
+          <t>有限会社オガワ商事</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>https://maruzen-group.jp/groups/234/</t>
-        </is>
-      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>大分県大分市上戸次732-1</t>
+          <t>大分県中津市大字相原3032-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>097-595-1088</t>
+          <t>0979-25-0260</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://maruzen-group.jp/contact/</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>有限会社篠原興業</t>
+          <t>有限会社翔樹</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://shinoharakogyo.com/</t>
+          <t>https://www.shoki-base-888.com/company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>大分県大分市上田町2丁目2番25号</t>
+          <t>大分県中津市大字福島1587番地1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>097-544-6928</t>
+          <t>0979-33-1078</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://shinoharakogyo.com/pages/5/</t>
+          <t>https://www.shoki-base-888.com/contact</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>有限会社ダイアン</t>
+          <t>株式会社ジャパンライン</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>大分県大分市下宗方946番地の2</t>
+          <t>大分県中津市大字福島740番地の2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -794,56 +742,68 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>株式会社フクダイ運輸</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+          <t>株式会社桜瀬運輸</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>all.right@hi3.enjoy.ne.jp</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>https://all-right-dream.com/</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>大分県大分市下戸次1527-1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>大分県中津市大字福島745番地の5</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0979-33-7807</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://all-right-dream.com/#contact</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>藤澤環境開発株式会社</t>
+          <t>有限会社山中陸送</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>https://www.fujisawa-eco.co.jp/</t>
-        </is>
-      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>大分県大分市久原中央4丁目7番1号</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>097-593-4211</t>
-        </is>
-      </c>
+          <t>大分県中津市大字福島910</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>株式会社エス・イー・アレックス</t>
+          <t>マルナカ物流株式会社</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>https://marunaka-butsuryu.jp/</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>大分県大分市乙津町3-1</t>
+          <t>大分県中津市大字福島字新開450番9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -853,213 +813,169 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>株式会社葵</t>
+          <t>有限会社扇運輸</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>https://aoikaikan.co.jp/</t>
-        </is>
-      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>大分県大分市住吉町1丁目3-45</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>097-534-0012</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/aoi.kaikan</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://aoikaikan.co.jp/contact_form/</t>
-        </is>
-      </c>
+          <t>大分県中津市大字鍋島830-1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>株式会社エーストランスポート</t>
+          <t>株式会社髙倉興業</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>http://www.acetransport.jp/</t>
+          <t>https://takakurakogyo.com/</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>大分県大分市佐野4294番地</t>
+          <t>大分県中津市山国町平小野91番地1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>097-524-2271</t>
+          <t>0979-62-3228</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>http://www.acetransport.jp/contact.php</t>
+          <t>https://takakurakogyo.com/contact/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>株式会社ゼウス</t>
+          <t>株式会社古園運送</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>https://www.zeus-oita.co.jp/</t>
-        </is>
-      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>大分県大分市勢家春日浦843-175</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>097-535-0585</t>
-        </is>
-      </c>
+          <t>大分県中津市福島1080番地3</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.zeus-oita.co.jp/contact/</t>
-        </is>
-      </c>
+      <c r="G21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>大豊運輸有限会社</t>
+          <t>神栄運送有限会社</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>http://www.taihou-unyu.jp/</t>
-        </is>
-      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>大分県大分市南春日町8−7</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>097-573-6862</t>
-        </is>
-      </c>
+          <t>大分県佐伯市9036-8</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.taihou-unyu.jp/tel.php</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>クリスタルシティータクシー株式会社</t>
+          <t>日昇運輸株式会社</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://ojk-citytaxi.jp/hearse/</t>
+          <t>http://www.saiki.tv/~nisho-usg/index.html</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>大分県大分市原川2丁目3番4号</t>
+          <t>大分県佐伯市上浦大字浅海井浦2394</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>097-503-4343</t>
+          <t>0972-32-3388</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://ojk-citytaxi.jp/contact/</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>三協通産株式会社</t>
+          <t>有限会社丸鮮運輸</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>https://sankyo-tetsu.co.jp/</t>
-        </is>
-      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>大分県大分市原川3-1-49</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>097-552-1539</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/san_tetsu3923</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://sankyo-tetsu.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>大分県佐伯市上灘区9849-1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>岡村システムサービス有限会社</t>
+          <t>株式会社アイエヌロジスティクス</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>https://inl1926.jp/network/</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>大分県大分市原新町13-6</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+          <t>大分県佐伯市大字上岡2768番1</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0972-28-5255</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/inl1926</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://inl1926.jp/contact-2/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>有限会社大分丸果運輸</t>
+          <t>丸英運輸株式会社</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>大分県大分市原新町7-10</t>
+          <t>大分県佐伯市大字木立永野2127番5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -1069,73 +985,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>浮城建機株式会社</t>
+          <t>株式会社番匠</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>大分県大分市向原沖1丁目1番22号</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>大分県佐伯市大字池田1326番地</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0120-907-108</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>有限会社大平運輸</t>
+          <t>有限会社伯友</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>大分県大分市向原沖1丁目1番41号</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>097-551-2296</t>
-        </is>
-      </c>
+          <t>大分県佐伯市大字池田777</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>株式会社トキハ物流サービス</t>
+          <t>株式会社UTT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://j7i2iuw91.jbplt.jp/</t>
+          <t>https://kaizaki.saiki.jp/utt/</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>大分県大分市向原沖1丁目2-14</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>大分県佐伯市大字海崎3648番地11</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>097-538-3221</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://kaizaki.saiki.jp/utt/inquiry/index.html</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>有限会社ジェット輸送</t>
+          <t>有限会社YAMAMURA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>大分県大分市向原沖2丁目2-22</t>
+          <t>大分県佐伯市大字海崎74番地</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1145,14 +1069,14 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>丸高産業運輸株式会社</t>
+          <t>新生総合株式会社</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>大分県大分市向原西1-7-39</t>
+          <t>大分県佐伯市大字海崎848-1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1162,43 +1086,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>安心院運輸株式会社</t>
+          <t>有限会社青山</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>https://www.big-advance.site/s/160/1567</t>
-        </is>
-      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>大分県大分市向原西1丁目4番5号</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>097-558-6555</t>
-        </is>
-      </c>
+          <t>大分県佐伯市大字青山5618番地1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.big-advance.site/c/160/1567/contact</t>
-        </is>
-      </c>
+      <c r="G32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>株式会社サンワ運輸</t>
+          <t>廣瀨産業株式会社</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>大分県大分市向原西2丁目2-11</t>
+          <t>大分県佐伯市大字鶴望4308番地1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
@@ -1208,14 +1120,14 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>有限会社幸運</t>
+          <t>緑通商有限会社</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>大分県大分市向原西2丁目5-30</t>
+          <t>大分県佐伯市宇目大字南田原584-3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1225,80 +1137,56 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>実鷹合同会社</t>
+          <t>東明運送有限会社</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.mitaka2020.com/</t>
+          <t>https://oita.tellogs.com/i3036939</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>大分県大分市坂ノ市4丁目2番11号野村ビル2階</t>
+          <t>大分県佐伯市宇目大字小野市4973-1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>097-511-5825</t>
+          <t>0972-54-3617</t>
         </is>
       </c>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.mitaka2020.com/contact</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>有限会社ニチヒロ運輸</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>nichihiro@sepia.ocn.ne.jp</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>https://www.nichihiro.com/</t>
-        </is>
-      </c>
+          <t>宇目運送有限会社</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>大分県大分市城原1897-12</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>097-529-8841</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nichihiro_unyu</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.nichihiro.com/%e3%81%8a%e5%95%8f%e3%81%84%e5%90%88%e3%82%8f%e3%81%9b/</t>
-        </is>
-      </c>
+          <t>大分県佐伯市宇目大字重岡503番地の1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ウエアハウス有限会社</t>
+          <t>株式会社纏三矢</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>大分県大分市大分流通業務団地2丁目1番</t>
+          <t>大分県佐伯市弥生大字井崎50番地</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
@@ -1308,93 +1196,69 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>トーショー九州株式会社</t>
+          <t>新和運送株式会社</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>https://www.tohsho-gr.co.jp/company/tohsho-kyushu/</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>大分県大分市大分流通業務団地2丁目4番</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>097-528-9118</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tohsho_group</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.tohsho-gr.co.jp/contact/kyushu/</t>
-        </is>
-      </c>
+          <t>大分県佐伯市弥生大字床木120番地</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>株式会社九州ロジスティクス</t>
+          <t>有限会社リュウエイ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>https://www.jrf-kyushu.co.jp/</t>
-        </is>
-      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>大分県大分市大在北3丁目140</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>大分県佐伯市弥生大字細田809-1</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0972-46-3132</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.jrf-kyushu.co.jp/inquiry.html</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>株式会社秀観</t>
+          <t>西武陸運有限会社</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>大分県大分市大在浜2丁目2-5</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>097-524-3711</t>
-        </is>
-      </c>
+          <t>大分県佐伯市田の浦町5-29</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>株式会社日豊建機運輸</t>
+          <t>有限会社中田運送</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>大分県大分市大字三佐2306-13</t>
+          <t>大分県佐伯市蒲江大字丸市尾浦1578-24</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1404,14 +1268,14 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>株式会社AT Group</t>
+          <t>株式会社北斗</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>大分県大分市大字三佐2306番地の1</t>
+          <t>大分県佐伯市蒲江大字葛原浦65</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
@@ -1421,18 +1285,14 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>大分松藤商事株式会社</t>
+          <t>有限会社イワモト</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>https://www.matsufuji-gr.com/group/land/office</t>
-        </is>
-      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>大分県大分市大字三佐大新田1354番地の5</t>
+          <t>大分県佐伯市西浜10834番地65</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
@@ -1442,147 +1302,155 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>大分運送株式会社</t>
+          <t>ポートラインサービス有限会社</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.matsufuji-gr.com/group/land/office</t>
+          <t>https://aomono-shop.jp/user_data/company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>大分県大分市大字三佐大新田1354番地の5</t>
+          <t>大分県佐伯市鶴見大字地松浦251-14</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>097-527-2280</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+          <t>0972-28-5599</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sakana20years</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://aomono-shop.jp/contact</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>東洋瓦斯株式会社</t>
+          <t>引越革命九州株式会社</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://cabosugas.com/</t>
+          <t>https://www.2020.co.jp/kyusyu</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>大分県大分市大字三佐字大新田1354-5</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>大分県別府市古市町881番地187</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0120-443-677</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>オーライン株式会社</t>
+          <t>株式会社鶴見運送</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://oyamakinzoku-group.com/group/</t>
+          <t>https://tsurumi-logi.com/about/index.html#outline</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>大分県大分市大字三佐字大新田1354番地の8</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>097-521-1170</t>
-        </is>
-      </c>
+          <t>大分県別府市大字鶴見67-2</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://oyamakinzoku-group.com/contact/index.html</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>有限会社龍成工業</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>株式会社鶴見</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>info@tsurumi-logi.com</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://ryusei-oita.jp/</t>
+          <t>http://tsurumi-logi.com/</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>大分県大分市大字上判田5487番地22</t>
+          <t>大分県別府市新別府町42−67−2</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>097-511-3564</t>
+          <t>0977-67-1661</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://ryusei-oita.jp/pages/5/</t>
+          <t>http://tsurumi-logi.com/information/inquiry/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>日本連合警備株式会社</t>
+          <t>株式会社共同運輸</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>http://www.renkei-oita.co.jp/</t>
+          <t>https://miura-gr.com/</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>大分県大分市大字上宗方字明川原124-1</t>
+          <t>大分県国東市国東町鶴川1623-1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>097-542-4711</t>
+          <t>097-547-8001</t>
         </is>
       </c>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://miura-gr.com/%e3%81%8a%e5%95%8f%e3%81%84%e5%90%88%e3%82%8f%e3%81%9b/</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>有限会社ドリームライン</t>
+          <t>有限会社吉武運輸</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>https://dreamline24.com/</t>
-        </is>
-      </c>
+      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>大分県大分市大字下判田2315-1</t>
+          <t>大分県国東市国東町鶴川24-4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
@@ -1592,68 +1460,64 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>有限会社阿南建材</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>有限会社フクミコーポレーション</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fukumi@oct-net.ne.jp</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.anankenzai.com/</t>
+          <t>https://www.fukumicorporation.com/</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>大分県大分市大字下判田2832</t>
+          <t>大分県国東市武蔵町小城51-15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>097-597-5176</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/anan.kenzai</t>
-        </is>
-      </c>
+          <t>0978-69-0180</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.anankenzai.com/contact</t>
+          <t>https://www.fukumicorporation.com</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>中央運送有限会社</t>
+          <t>有限会社椎原急配</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>大分県大分市大字下戸次1363</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>097-597-1232</t>
-        </is>
-      </c>
+          <t>大分県大分市ひばりケ丘3丁目9番2号</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>昭和産業有限会社</t>
+          <t>株式会社FIRST EXPRESS</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>大分県大分市大字中の洲2</t>
+          <t>大分県大分市三川新町2丁目1番8号</t>
         </is>
       </c>
       <c r="E52" t="inlineStr"/>
@@ -1663,68 +1527,60 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>株式会社サトー運輸</t>
+          <t>トランステック九州有限会社</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>https://sato-u.com/company/</t>
-        </is>
-      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>大分県大分市大字中戸次1261-93</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>097-597-4847</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/sato_unnyu_official</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://sato-u.com/contact/</t>
-        </is>
-      </c>
+          <t>大分県大分市上戸次3681</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>有限会社彗成物流</t>
+          <t>大分丸善運輸株式会社</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>https://maruzen-group.jp/groups/234/</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>大分県大分市大字中戸次1261番地の33</t>
+          <t>大分県大分市上戸次732-1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>097-598-0303</t>
+          <t>097-595-1088</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://maruzen-group.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>有限会社東武運輸</t>
+          <t>有限会社ダイアン</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>大分県大分市大字中戸次5879-1</t>
+          <t>大分県大分市下宗方946番地の2</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -1734,43 +1590,43 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>株式会社中部輸送</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
+          <t>株式会社フクダイ運輸</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>fukudaiunyu.s@gmail.com</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://chubu-yuso.com/</t>
+          <t>https://www.fukudai-trans.co.jp/</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>大分県大分市大字中戸次6093番地1</t>
+          <t>大分県大分市下戸次1527-1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>097-548-8256</t>
+          <t>097-574-4038</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://chubu-yuso.com/index.html#CONTACT</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>株式会社SMS.LINE</t>
+          <t>株式会社エス・イー・アレックス</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>大分県大分市大字中戸次字中峯906番地の3</t>
+          <t>大分県大分市乙津町3-1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -1780,114 +1636,134 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>有限会社中央産業輸送</t>
+          <t>株式会社エーストランスポート</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>http://www.acetransport.jp/</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>大分県大分市大字丹川1901番地の2</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
+          <t>大分県大分市佐野4294番地</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>097-524-2271</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>http://www.acetransport.jp/contact.php</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>株式会社三興</t>
+          <t>株式会社ゼウス</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>https://www.zeus-oita.co.jp/</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>大分県大分市大字丹生30番地41</t>
+          <t>大分県大分市勢家春日浦843-175</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>097-592-1289</t>
+          <t>097-535-0585</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.zeus-oita.co.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ニューテクノファースト株式会社</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>manager@ntf-inc.com</t>
-        </is>
-      </c>
+          <t>大豊運輸有限会社</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>http://ntf-corp.com/company/</t>
+          <t>http://www.taihou-unyu.jp/</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>大分県大分市大字丹生473-1</t>
+          <t>大分県大分市南春日町8−7</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>097-592-5000</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/newtechnofirst</t>
-        </is>
-      </c>
+          <t>097-573-6862</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://ntf-corp.com/contact2/</t>
+          <t>https://www.taihou-unyu.jp/tel.php</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>新生運送株式会社</t>
+          <t>三協通産株式会社</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>http://www.shinsei-unsou.jp/</t>
+          <t>https://sankyo-tetsu.co.jp/</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>大分県大分市大字南字石原283-1</t>
+          <t>大分県大分市原川3-1-49</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>097-522-1238</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+          <t>097-552-1539</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/san_tetsu3923</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://sankyo-tetsu.co.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>株式会社シンコー</t>
+          <t>岡村システムサービス有限会社</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>大分県大分市大字国分1973番地18</t>
+          <t>大分県大分市原新町13-6</t>
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
@@ -1897,39 +1773,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ホーヨ運輸有限会社</t>
+          <t>有限会社大分丸果運輸</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>https://hoyounyu.co.jo/</t>
-        </is>
-      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
-          <t>大分県大分市大字城原215番地の3</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>097-593-0404</t>
-        </is>
-      </c>
+          <t>大分県大分市原新町7-10</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>黒洋建設工業株式会社</t>
+          <t>有限会社大平運輸</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr">
         <is>
-          <t>大分県大分市大字城原2376番地</t>
+          <t>大分県大分市向原沖1丁目1番41号</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -1939,359 +1807,331 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>株式会社大興吊運</t>
+          <t>株式会社トキハ物流サービス</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://daikochoun.com/</t>
+          <t>https://j7i2iuw91.jbplt.jp/</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>大分県大分市大字城原644番地の6</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>097-574-7765</t>
-        </is>
-      </c>
+          <t>大分県大分市向原沖1丁目2-14</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://daikochoun.com/contact/</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>新和運輸有限会社</t>
+          <t>有限会社ジェット輸送</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
-          <t>大分県大分市大字城原字蓮池2404-1</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>097-593-3103</t>
-        </is>
-      </c>
+          <t>大分県大分市向原沖2丁目2-22</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>一番運輸株式会社</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>n-fujita@1van.co.jp</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>http://www.1van.co.jp/</t>
-        </is>
-      </c>
+          <t>丸高産業運輸株式会社</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>大分県大分市大字大在2</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>097-593-1177</t>
-        </is>
-      </c>
+          <t>大分県大分市向原西1-7-39</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>大分海陸運送株式会社</t>
+          <t>安心院運輸株式会社</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://oita-kairiku.co.jp/</t>
+          <t>https://www.big-advance.site/s/160/1567</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>大分県大分市大字大在2</t>
+          <t>大分県大分市向原西1丁目4番5号</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>097-593-5577</t>
+          <t>097-558-6555</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://oita-kairiku.co.jp/contact/</t>
+          <t>https://www.big-advance.site/c/160/1567/contact</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>株式会社北大</t>
+          <t>株式会社サンワ運輸</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>http://www.e-hokudai.jp/</t>
-        </is>
-      </c>
+      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
-          <t>大分県大分市大字大在2</t>
+          <t>大分県大分市向原西2丁目2-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>097-592-4646</t>
+          <t>097-551-0735</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.e-hokudai.jp/contact/</t>
-        </is>
-      </c>
+      <c r="G69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>株式会社大分丸運</t>
+          <t>実鷹合同会社</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.maruwn.co.jp/group/about/oitamaruwn/</t>
+          <t>https://www.mitaka2020.com/</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>大分県大分市大字大在2</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
+          <t>大分県大分市坂ノ市4丁目2番11号野村ビル2階</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>097-511-5825</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.mitaka2020.com/contact</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>臼杵運送株式会社</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>有限会社ニチヒロ運輸</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>nichihiro@sepia.ocn.ne.jp</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.usukiunso.co.jp/</t>
+          <t>https://www.nichihiro.com/</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>大分県大分市大字大在2</t>
+          <t>大分県大分市城原1897-12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>097-593-1001</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+          <t>097-529-8841</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nichihiro_unyu</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.nichihiro.com/%e3%81%8a%e5%95%8f%e3%81%84%e5%90%88%e3%82%8f%e3%81%9b/</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>鶴海運輸株式会社</t>
+          <t>ウエアハウス有限会社</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>http://www.turu-un.jp/</t>
+          <t>https://warehouse-oita.com/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>大分県大分市大字大在2番11</t>
+          <t>大分県大分市大分流通業務団地2丁目1番</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>097-592-0116</t>
+          <t>097-592-0777</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://warehouse-oita.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>鶴崎海陸運輸株式会社</t>
+          <t>トーショー九州株式会社</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.tsurukai.co.jp/</t>
+          <t>https://www.tohsho-gr.co.jp/company/tohsho-kyushu/</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>大分県大分市大字大在2番3</t>
+          <t>大分県大分市大分流通業務団地2丁目4番</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0979-27-6162</t>
+          <t>097-528-9118</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/tsurukai0418</t>
+          <t>https://www.instagram.com/tohsho_group</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.tsurukai.co.jp/contact-access/</t>
+          <t>https://www.tohsho-gr.co.jp/contact/kyushu/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>株式会社大分海陸</t>
+          <t>株式会社九州ロジスティクス</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>http://www.oita-kairiku.co.jp/</t>
+          <t>https://www.jrf-kyushu.co.jp/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>大分県大分市大字大在2番地</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>097-593-5577</t>
-        </is>
-      </c>
+          <t>大分県大分市大在北3丁目140</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://oita-kairiku.co.jp/contact/</t>
+          <t>https://www.jrf-kyushu.co.jp/inquiry.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>有限会社柏原商店</t>
+          <t>株式会社秀観</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>大分県大分市大字大津留160-2</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>大分県大分市大在浜2丁目2-5</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>097-524-3711</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>株式会社一休</t>
+          <t>株式会社日豊建機運輸</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>https://www.funeral-ikkyu.com/</t>
-        </is>
-      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>大分県大分市大字奥田500番地の4</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>0120-097-544</t>
-        </is>
-      </c>
+          <t>大分県大分市大字三佐2306-13</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.funeral-ikkyu.com/access/</t>
-        </is>
-      </c>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>東九州デイリーフーヅ株式会社</t>
+          <t>株式会社AT Group</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>https://dailyfoods.jp/</t>
-        </is>
-      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>大分県大分市大字家島1229番地1</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>097-574-8175</t>
-        </is>
-      </c>
+          <t>大分県大分市大字三佐2306番地の1</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://dailyfoods.jp/#contact</t>
-        </is>
-      </c>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>有限会社髙瀬商運</t>
+          <t>大分松藤商事株式会社</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.matsufuji-gr.com/group/land/office</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>大分県大分市大字家島665番地の1ベルフロント家島102</t>
+          <t>大分県大分市大字三佐大新田1354番地の5</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2301,19 +2141,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>有限会社梅木工業</t>
+          <t>大分運送株式会社</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.matsufuji-gr.com/group/land/office</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>大分県大分市大字寒田232-18</t>
+          <t>大分県大分市大字三佐大新田1354番地の5</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>097-568-0422</t>
+          <t>097-527-2280</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -2322,31 +2166,47 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>三宮運送有限会社</t>
+          <t>オーライン株式会社</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr"/>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://oyamakinzoku-group.com/group/</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>大分県大分市大字小池原1200番地の1</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr"/>
+          <t>大分県大分市大字三佐字大新田1354番地の8</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>097-521-1170</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://oyamakinzoku-group.com/contact/index.html</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>株式会社エクシト</t>
+          <t>有限会社ドリームライン</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://dreamline24.com/</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>大分県大分市大字常行87番地の2</t>
+          <t>大分県大分市大字下判田2315-1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2356,98 +2216,118 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>株式会社トランスネットワーク</t>
+          <t>有限会社阿南建材</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>http://transnetwork.co.jp/</t>
+          <t>https://www.anankenzai.com/</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>大分県大分市大字廻栖野2188番地</t>
+          <t>大分県大分市大字下判田2832</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>097-588-1702</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
+          <t>097-597-5176</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/anan.kenzai</t>
+        </is>
+      </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://transnetwork.co.jp/contact</t>
+          <t>https://www.anankenzai.com/contact</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>有限会社平神工業</t>
+          <t>中央運送有限会社</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>大分県大分市大字廻栖野2510-1</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr"/>
+          <t>大分県大分市大字下戸次1363</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>097-597-1232</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>みどり運送株式会社</t>
+          <t>昭和産業有限会社</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>大分県大分市大字廻栖野3231</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>097-586-4187</t>
-        </is>
-      </c>
+          <t>大分県大分市大字中の洲2</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>株式会社マルカツ工業</t>
+          <t>株式会社サトー運輸</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://sato-u.com/company/</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>大分県大分市大字志村367番地の1</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr"/>
+          <t>大分県大分市大字中戸次1261-93</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>097-597-4847</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sato_unnyu_official</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://sato-u.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>有限会社九州豊予運輸</t>
+          <t>有限会社彗成物流</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
-          <t>大分県大分市大字志生木1319番地</t>
+          <t>大分県大分市大字中戸次1261番地の33</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2457,72 +2337,60 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>株式会社カトーロジック</t>
+          <t>有限会社東武運輸</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>https://katologic.com/</t>
-        </is>
-      </c>
+      <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>大分県大分市大字曲1124番地の1</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>097-529-7410</t>
-        </is>
-      </c>
+          <t>大分県大分市大字中戸次5879-1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
       <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://katologic.com/contact</t>
-        </is>
-      </c>
+      <c r="G87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>株式会社うるま優交社</t>
+          <t>株式会社中部輸送</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.osogi.co.jp/</t>
+          <t>https://chubu-yuso.com/</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>大分県大分市大字木上409-3</t>
+          <t>大分県大分市大字中戸次6093番地1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>097-567-0983</t>
+          <t>097-548-8256</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.osogi.co.jp/toiawase.html</t>
+          <t>https://chubu-yuso.com/index.html#CONTACT</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>有限会社片桐設備</t>
+          <t>株式会社SMS.LINE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>大分県大分市大字木田831番地の6</t>
+          <t>大分県大分市大字中戸次字中峯906番地の3</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2532,39 +2400,31 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>日成運送株式会社</t>
+          <t>有限会社中央産業輸送</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>https://nissei-unso.com/</t>
-        </is>
-      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>大分県大分市大字松岡2058番地の1</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>097-520-1112</t>
-        </is>
-      </c>
+          <t>大分県大分市大字丹川1901番地の2</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>株式会社クローバー</t>
+          <t>株式会社三興</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>大分県大分市大字松岡3554番地の1</t>
+          <t>大分県大分市大字丹生30番地41</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2574,102 +2434,102 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>清栄開発株式会社</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>ニューテクノファースト株式会社</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>manager@ntf-inc.com</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>https://www.seiei11.com/company</t>
+          <t>http://ntf-corp.com/company/</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>大分県大分市大字松岡5162番地の1</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+          <t>大分県大分市大字丹生473-1</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>097-592-5000</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/newtechnofirst</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://ntf-corp.com/contact2/</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>株式会社SKサービス</t>
+          <t>新生運送株式会社</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>https://www.skservice-1016.com/company</t>
+          <t>http://www.shinsei-unsou.jp/</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>大分県大分市大字横塚2丁目208番地</t>
+          <t>大分県大分市大字南字石原283-1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>097-592-1114</t>
+          <t>097-522-1238</t>
         </is>
       </c>
       <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.skservice-1016.com/contact</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>株式会社今吉機設</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>info@imayoshikisetsu.co.jp</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>http://www.imayoshikisetsu.co.jp/company.html</t>
-        </is>
-      </c>
+          <t>株式会社シンコー</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>大分県大分市大字横尾3104番地の16</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>097-520-0054</t>
-        </is>
-      </c>
+          <t>大分県大分市大字国分1973番地18</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr"/>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>http://www.imayoshikisetsu.co.jp/contact.html</t>
-        </is>
-      </c>
+      <c r="G94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>大野運送株式会社</t>
+          <t>ホーヨ運輸有限会社</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://hoyounyu.co.jo/</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>大分県大分市大字横瀬1017</t>
+          <t>大分県大分市大字城原215番地の3</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>097-542-0658</t>
+          <t>097-593-0404</t>
         </is>
       </c>
       <c r="F95" t="inlineStr"/>
@@ -2678,151 +2538,151 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>田島運輸株式会社</t>
+          <t>株式会社大興吊運</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>http://www.oct-net.ne.jp/sangyo/company/</t>
+          <t>https://daikochoun.com/</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>大分県大分市大字横田31番地</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
+          <t>大分県大分市大字城原644番地の6</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>097-574-7765</t>
+        </is>
+      </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://daikochoun.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>株式会社スズキ</t>
+          <t>新和運輸有限会社</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>https://e-suzuki.co.jp/ja/</t>
-        </is>
-      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
-          <t>大分県大分市大字毛井818-1</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>097-520-1414</t>
-        </is>
-      </c>
+          <t>大分県大分市大字城原字蓮池2404-1</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>株式会社ビッグウェーブカワサキ</t>
+          <t>一番運輸株式会社</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>kawasaki-01@bigwave-net.co.jp</t>
+          <t>n-fujita@1van.co.jp</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>https://www.bw-kawasaki.jp/company/</t>
+          <t>http://www.1van.co.jp/</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>大分県大分市大字津守389番地の8</t>
+          <t>大分県大分市大字大在2</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>097-569-3360</t>
+          <t>097-593-1177</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.bw-kawasaki.jp/inquiry/</t>
-        </is>
-      </c>
+      <c r="G98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>江藤運輸株式会社</t>
+          <t>大分海陸運送株式会社</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>https://www.etosanso.co.jp/group/index.html</t>
+          <t>https://oita-kairiku.co.jp/</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>大分県大分市大字海原字新田1005-7</t>
+          <t>大分県大分市大字大在2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>097-522-3751</t>
+          <t>097-593-5577</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.etosanso.co.jp/contact/index.html</t>
+          <t>https://oita-kairiku.co.jp/contact/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>有限会社豊成相互運輸</t>
+          <t>株式会社北大</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>https://seiko-group.jp/service/index05.html</t>
+          <t>http://www.e-hokudai.jp/</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>大分県大分市大字片島1436番地の2</t>
+          <t>大分県大分市大字大在2</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>097-568-1113</t>
+          <t>097-592-4646</t>
         </is>
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://seiko-group.jp/contact/</t>
+          <t>https://www.e-hokudai.jp/contact/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>株式会社祐徳</t>
+          <t>株式会社大分丸運</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
-      <c r="C101" t="inlineStr"/>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.maruwn.co.jp/group/about/oitamaruwn/</t>
+        </is>
+      </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>大分県大分市大字片島1693番地の1</t>
+          <t>大分県大分市大字大在2</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -2832,131 +2692,147 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>株式会社東陽企画</t>
+          <t>鶴海運輸株式会社</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>https://watanabegroup.jp/toyo.html</t>
+          <t>http://www.turu-un.jp/</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>大分県大分市大字片島1807番地</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr"/>
+          <t>大分県大分市大字大在2番11</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>097-592-0116</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>有限会社ダイソー環境開発</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>info@e-daiso.com</t>
-        </is>
-      </c>
+          <t>鶴崎海陸運輸株式会社</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>http://www.e-daiso.com/</t>
+          <t>https://www.tsurukai.co.jp/</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>大分県大分市大字片島2995番地の5</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
+          <t>大分県大分市大字大在2番3</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0979-27-6162</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tsurukai0418</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.e-daiso.com/contact/index.html</t>
+          <t>https://www.tsurukai.co.jp/contact-access/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>三光運輸株式会社</t>
+          <t>株式会社大分海陸</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
-      <c r="C104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>http://www.oita-kairiku.co.jp/</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>大分県大分市大字種具1056</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr"/>
+          <t>大分県大分市大字大在2番地</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>097-593-5577</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
-      <c r="G104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://oita-kairiku.co.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>さくら運輸株式会社</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>sakura-saiki@estate.ocn.ne.jp</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>https://sakura-sd.jp/</t>
-        </is>
-      </c>
+          <t>有限会社柏原商店</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
-          <t>大分県大分市大字種具1394-1</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>097-528-1214</t>
-        </is>
-      </c>
+          <t>大分県大分市大字大津留160-2</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://sakura-sd.jp/pages/5/</t>
-        </is>
-      </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>株式会社髙橋重機運送</t>
+          <t>東九州デイリーフーヅ株式会社</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
-      <c r="C106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://dailyfoods.jp/</t>
+        </is>
+      </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>大分県大分市大字種具1402-1</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr"/>
+          <t>大分県大分市大字家島1229番地1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>097-574-8175</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
-      <c r="G106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://dailyfoods.jp/#contact</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>岩男工業株式会社</t>
+          <t>有限会社髙瀬商運</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
-          <t>大分県大分市大字種具728番地</t>
+          <t>大分県大分市大字家島665番地の1ベルフロント家島102</t>
         </is>
       </c>
       <c r="E107" t="inlineStr"/>
@@ -2966,39 +2842,31 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>九州ライトニング物流有限会社</t>
+          <t>三宮運送有限会社</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>https://www.klb-oita.com/index.html</t>
-        </is>
-      </c>
+      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
-          <t>大分県大分市大字種具字田代1164-1</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>097-503-6080</t>
-        </is>
-      </c>
+          <t>大分県大分市大字小池原1200番地の1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>有限会社大翔運輸</t>
+          <t>株式会社エクシト</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>大分県大分市大字竹矢1280</t>
+          <t>大分県大分市大字常行87番地の2</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -3008,52 +2876,64 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>西大分運送有限会社</t>
+          <t>株式会社トランスネットワーク</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>http://transnetwork.co.jp/</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>大分県大分市大字羽田191-15</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr"/>
+          <t>大分県大分市大字廻栖野2188番地</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>097-588-1702</t>
+        </is>
+      </c>
       <c r="F110" t="inlineStr"/>
-      <c r="G110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://transnetwork.co.jp/contact</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>有限会社大分新聞輸送</t>
+          <t>みどり運送株式会社</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
-          <t>大分県大分市大字荏隈字庄の原1849-32</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr"/>
+          <t>大分県大分市大字廻栖野3231</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>097-586-4187</t>
+        </is>
+      </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>大分総合運輸株式会社</t>
+          <t>有限会社九州豊予運輸</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>http://www.oita-sogo-unyu.co.jp/</t>
-        </is>
-      </c>
+      <c r="C112" t="inlineStr"/>
       <c r="D112" t="inlineStr">
         <is>
-          <t>大分県大分市大字荏隈字庄ノ原2組の4</t>
+          <t>大分県大分市大字志生木1319番地</t>
         </is>
       </c>
       <c r="E112" t="inlineStr"/>
@@ -3063,72 +2943,68 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>日鉄物流大分株式会社</t>
+          <t>株式会社カトーロジック</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>https://www.log.nipponsteel.com/about_us/executive/</t>
+          <t>https://katologic.com/</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>大分県大分市大字西ノ洲1番地</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr"/>
+          <t>大分県大分市大字曲1124番地の1</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>097-529-7410</t>
+        </is>
+      </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.log.nipponsteel.com/inquiry/</t>
+          <t>https://katologic.com/contact</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>豊和通商有限会社</t>
+          <t>日成運送株式会社</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>https://shs-group.jp/company/</t>
+          <t>https://nissei-unso.com/</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>大分県大分市大字角子原857-1</t>
+          <t>大分県大分市大字松岡2058番地の1</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>097-523-0883</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/shsgroup_511</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://shs-group.jp/contact/</t>
-        </is>
-      </c>
+          <t>097-520-1112</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>詫磨開発株式会社</t>
+          <t>株式会社クローバー</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>大分県大分市大字迫311番地の1</t>
+          <t>大分県大分市大字松岡3554番地の1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
@@ -3138,52 +3014,68 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>有限会社KOKEN大分</t>
+          <t>株式会社SKサービス</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>https://www.skservice-1016.com/company</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>大分県大分市大字迫386番地の3</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr"/>
+          <t>大分県大分市大字横塚2丁目208番地</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>097-592-1114</t>
+        </is>
+      </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.skservice-1016.com/contact</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>有限会社幸建企画</t>
+          <t>大野運送株式会社</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>https://www.koukenkikaku.jp/</t>
-        </is>
-      </c>
+      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
-          <t>大分県大分市大字迫386番地の3</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr"/>
+          <t>大分県大分市大字横瀬1017</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>097-542-0658</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>有限会社ムラセ運輸</t>
+          <t>田島運輸株式会社</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>http://www.oct-net.ne.jp/sangyo/company/</t>
+        </is>
+      </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>大分県大分市大字迫538-2</t>
+          <t>大分県大分市大字横田31番地</t>
         </is>
       </c>
       <c r="E118" t="inlineStr"/>
@@ -3193,123 +3085,139 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>東九州運輸有限会社</t>
+          <t>株式会社スズキ</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>https://e-suzuki.co.jp/ja/</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>大分県大分市大字迫925-3</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr"/>
+          <t>大分県大分市大字毛井818-1</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>097-520-1414</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>株式会社雅工業</t>
+          <t>江藤運輸株式会社</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>https://www.big-advance.site/s/207/1278</t>
+          <t>https://www.etosanso.co.jp/group/index.html</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>大分県大分市大字迫9番地の106</t>
+          <t>大分県大分市大字海原字新田1005-7</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>097-574-9449</t>
+          <t>097-522-3751</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.big-advance.site/c/207/1278/contact</t>
+          <t>https://www.etosanso.co.jp/contact/index.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>有限会社東輝工業</t>
+          <t>有限会社豊成相互運輸</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
-      <c r="C121" t="inlineStr"/>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>https://seiko-group.jp/service/index05.html</t>
+        </is>
+      </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>大分県大分市大字迫字丸山658-2</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr"/>
+          <t>大分県大分市大字片島1436番地の2</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>097-568-1113</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://seiko-group.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>株式会社マテリアルデポット</t>
+          <t>株式会社祐徳</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>http://www.m-depot.biz/</t>
-        </is>
-      </c>
+      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>大分県大分市大字迫字新殿776-1</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>097-576-7518</t>
-        </is>
-      </c>
+          <t>大分県大分市大字片島1693番地の1</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr"/>
       <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.m-depot.biz/contact/</t>
-        </is>
-      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>株式会社竜翔</t>
+          <t>株式会社東陽企画</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr"/>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>https://watanabegroup.jp/toyo.html</t>
+        </is>
+      </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>大分県大分市大字里1350番地の4</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr"/>
+          <t>大分県大分市大字片島1807番地</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>097-578-8832</t>
+        </is>
+      </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>株式会社明日香会館</t>
+          <t>三光運輸株式会社</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
-          <t>大分県大分市大字里451番地</t>
+          <t>大分県大分市大字種具1056</t>
         </is>
       </c>
       <c r="E124" t="inlineStr"/>
@@ -3319,280 +3227,256 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>東九総合運輸株式会社</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr"/>
+          <t>さくら運輸株式会社</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>sakura-saiki@estate.ocn.ne.jp</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>http://tokyu-sogo.co.jp/</t>
+          <t>https://sakura-sd.jp/</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>大分県大分市大字駄原2905番10</t>
+          <t>大分県大分市大字種具1394-1</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>097-533-2253</t>
+          <t>097-528-1214</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://sakura-sd.jp/pages/5/</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>株式会社ガスエネルギー大分</t>
+          <t>株式会社髙橋重機運送</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>https://gas-energy-oita.com/</t>
-        </is>
-      </c>
+      <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>大分県大分市大字駄原字豊久北浦2898-1</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>097-534-0540</t>
-        </is>
-      </c>
+          <t>大分県大分市大字種具1402-1</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>有限会社リサイクルテクノロジー</t>
+          <t>九州ライトニング物流有限会社</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>http://risateku.com/</t>
+          <t>https://www.klb-oita.com/index.html</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>大分県大分市大字鴛野247番地</t>
+          <t>大分県大分市大字種具字田代1164-1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>097-568-0367</t>
+          <t>097-503-6080</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>http://risateku.com/contact/contact.html</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>大分県急便株式会社</t>
+          <t>有限会社大翔運輸</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>https://oita-zakkan.seesaa.net/article/520415995.html</t>
+          <t>https://n-seikei.jp/2025/05/post-109946.html</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>大分県大分市大字鴛野826-1</t>
+          <t>大分県大分市大字竹矢1280</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>097-569-3340</t>
+          <t>097-588-1178</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>http://n-seikei.jp/contact.html</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>有限会社西岡商会</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>info@nishioka-shokai.com</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>https://www.nishioka-shokai.com/</t>
-        </is>
-      </c>
+          <t>西大分運送有限会社</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
-          <t>大分県大分市大字鴛野872-5</t>
+          <t>大分県大分市大字羽田191-15</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>097-569-6681</t>
+          <t>097-568-6332</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.nishioka-shokai.com/contact</t>
-        </is>
-      </c>
+      <c r="G129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>詫磨運輸株式会社</t>
+          <t>有限会社大分新聞輸送</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>https://www.takuma-group.com/company/transport.html</t>
-        </is>
-      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>大分県大分市大手町1丁目2番1号詫磨ビル2階</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>097-536-2775</t>
-        </is>
-      </c>
+          <t>大分県大分市大字荏隈字庄の原1849-32</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.takuma-group.com/contact/index.html</t>
-        </is>
-      </c>
+      <c r="G130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>鶴崎林商運輸株式会社</t>
+          <t>大分総合運輸株式会社</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>http://www.rinsyo.co.jp/</t>
+          <t>http://www.oita-sogo-unyu.co.jp/</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>大分県大分市小中島2丁目3-32</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>097-521-2231</t>
-        </is>
-      </c>
+          <t>大分県大分市大字荏隈字庄ノ原2組の4</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.rinsyo.co.jp/contact/</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>日豊運送株式会社</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>info@nippou-unso.com</t>
-        </is>
-      </c>
+          <t>日鉄物流大分株式会社</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>http://nippou-unso.com/</t>
+          <t>https://www.log.nipponsteel.com/about_us/executive/</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>大分県大分市小中島2丁目4-45</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>097-524-0066</t>
-        </is>
-      </c>
+          <t>大分県大分市大字西ノ洲1番地</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr">
         <is>
-          <t>http://nippou-unso.com/contact/</t>
+          <t>https://www.log.nipponsteel.com/inquiry/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>株式会社木崎運輸</t>
+          <t>豊和通商有限会社</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
-      <c r="C133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>https://shs-group.jp/company/</t>
+        </is>
+      </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>大分県大分市屋山595</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+          <t>大分県大分市大字角子原857-1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>097-523-0883</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shsgroup_511</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://shs-group.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>昭和運輸株式会社</t>
+          <t>有限会社KOKEN大分</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
-          <t>大分県大分市府内町3丁目5-4</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>097-532-1311</t>
-        </is>
-      </c>
+          <t>大分県大分市大字迫386番地の3</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>株式会社戸次急配</t>
+          <t>有限会社幸建企画</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>https://www.koukenkikaku.jp/</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>大分県大分市弁天2-5-35</t>
+          <t>大分県大分市大字迫386番地の3</t>
         </is>
       </c>
       <c r="E135" t="inlineStr"/>
@@ -3602,119 +3486,103 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>株式会社TAMAYA</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>logi@tmy-truck.jp</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>http://www.tamaya-yu.com/</t>
-        </is>
-      </c>
+          <t>有限会社ムラセ運輸</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>大分県大分市弁天2丁目4番36号</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>097-535-1771</t>
-        </is>
-      </c>
+          <t>大分県大分市大字迫538-2</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>トヨミ運輸株式会社</t>
+          <t>東九州運輸有限会社</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>https://oitakyoueikousan.com/%E3%83%88%E3%83%A8%E3%83%9F%E9%81%8B%E8%BC%B8%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BE/</t>
-        </is>
-      </c>
+      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
-          <t>大分県大分市弁天3丁目1-1</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>097-537-0502</t>
-        </is>
-      </c>
+          <t>大分県大分市大字迫925-3</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>日野陸運有限会社</t>
+          <t>株式会社マテリアルデポット</t>
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
-      <c r="C138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>http://www.m-depot.biz/</t>
+        </is>
+      </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>大分県大分市弁天3丁目1994-54</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>大分県大分市大字迫字新殿776-1</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>097-576-7518</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.m-depot.biz/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>トキワ運輸株式会社</t>
+          <t>株式会社竜翔</t>
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>https://tokiwa.jbplt.jp/</t>
-        </is>
-      </c>
+      <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr">
         <is>
-          <t>大分県大分市徳島3丁目1-15</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>097-521-3232</t>
-        </is>
-      </c>
+          <t>大分県大分市大字里1350番地の4</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>イトウライナー株式会社</t>
+          <t>東九総合運輸株式会社</t>
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>https://itoliner.com/</t>
+          <t>http://tokyu-sogo.co.jp/</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>大分県大分市新川町1丁目11-15-209</t>
+          <t>大分県大分市大字駄原2905番10</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>0120-939-208</t>
+          <t>097-533-2253</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -3723,293 +3591,297 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>株式会社TRANSPORT稔</t>
+          <t>大分県急便株式会社</t>
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>https://tp-zin.com/</t>
+          <t>https://oita-zakkan.seesaa.net/article/520415995.html</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>大分県大分市新栄町9番7-2号</t>
+          <t>大分県大分市大字鴛野826-1</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>097-579-6711</t>
+          <t>097-569-3340</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://tp-zin.com/toi.php</t>
-        </is>
-      </c>
+      <c r="G141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>上田重建有限会社</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr"/>
-      <c r="C142" t="inlineStr"/>
+          <t>有限会社西岡商会</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>info@nishioka-shokai.com</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>https://www.nishioka-shokai.com/</t>
+        </is>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>大分県大分市日岡2丁目1-31</t>
+          <t>大分県大分市大字鴛野872-5</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>097-558-2859</t>
+          <t>097-569-6681</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.nishioka-shokai.com/contact</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>株式会社センコーロード</t>
+          <t>詫磨運輸株式会社</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>http://beetle.co.jp/index.php</t>
+          <t>https://www.takuma-group.com/company/transport.html</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>大分県大分市東浜2-6-11</t>
+          <t>大分県大分市大手町1丁目2番1号詫磨ビル2階</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>097-547-8445</t>
+          <t>097-536-2775</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr">
         <is>
-          <t>http://beetle.co.jp/contact.html</t>
+          <t>https://www.takuma-group.com/contact/index.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>サンパワーシステム株式会社</t>
+          <t>鶴崎林商運輸株式会社</t>
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>http://www.rinsyo.co.jp/</t>
+        </is>
+      </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>大分県大分市東鶴崎3丁目2番10号</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr"/>
+          <t>大分県大分市小中島2丁目3-32</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>097-521-2231</t>
+        </is>
+      </c>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.rinsyo.co.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>有限会社慎運輸</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr"/>
-      <c r="C145" t="inlineStr"/>
+          <t>日豊運送株式会社</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>info@nippou-unso.com</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>http://nippou-unso.com/</t>
+        </is>
+      </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>大分県大分市横尾東町4丁目13番21号</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr"/>
+          <t>大分県大分市小中島2丁目4-45</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>097-524-0066</t>
+        </is>
+      </c>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>http://nippou-unso.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>日本貨物株式会社</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>info@nihonkamotsu.co.jp</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>https://www.nihonkamotsu.co.jp/</t>
-        </is>
-      </c>
+          <t>株式会社木崎運輸</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>大分県大分市牧1645-1</t>
+          <t>大分県大分市屋山595</t>
         </is>
       </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.nihonkamotsu.co.jp/contact.html</t>
-        </is>
-      </c>
+      <c r="G146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>有限会社金子土木建設</t>
+          <t>大富株式会社</t>
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>https://www.oh-tomi.co.jp/base.html</t>
+        </is>
+      </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>大分県大分市王子山の手町24番3号</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>097-560-5606</t>
-        </is>
-      </c>
+          <t>大分県大分市府内町2丁目3番25号コスモビル2階</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.oh-tomi.co.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>九州航空株式会社</t>
+          <t>昭和運輸株式会社</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>http://www.kyushu-aw.co.jp/salesoffice.html</t>
-        </is>
-      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>大分県大分市王子町12番1号</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/kyushu_airways.official</t>
-        </is>
-      </c>
+          <t>大分県大分市府内町3丁目5-4</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>097-532-1311</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>赤帽大分運送</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>akabouoita@air.ocn.ne.jp</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>https://www.oita-akabou.com/</t>
-        </is>
-      </c>
+          <t>株式会社戸次急配</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>大分県大分市生石40−4</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>0120-606-601</t>
-        </is>
-      </c>
+          <t>大分県大分市弁天2-5-35</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.oita-akabou.com</t>
-        </is>
-      </c>
+      <c r="G149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>住吉運輸産業株式会社</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr"/>
+          <t>株式会社TAMAYA</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>logi@tmy-truck.jp</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>https://www.seagatecorp.com/company/associated/</t>
+          <t>http://www.tamaya-yu.com/</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>大分県大分市生石5-3-1</t>
+          <t>大分県大分市弁天2丁目4番36号</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>097-534-3741</t>
+          <t>097-535-1771</t>
         </is>
       </c>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.seagatecorp.com/contact/</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>野津運送株式会社</t>
+          <t>トヨミ運輸株式会社</t>
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>https://notsu.jp/</t>
+          <t>https://oitakyoueikousan.com/%E3%83%88%E3%83%A8%E3%83%9F%E9%81%8B%E8%BC%B8%E6%A0%AA%E5%BC%8F%E4%BC%9A%E7%A4%BE/</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>大分県大分市畑中3丁目3番76号</t>
+          <t>大分県大分市弁天3丁目1-1</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>097-545-3623</t>
+          <t>097-537-0502</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://notsu.jp/toiawase/</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>有限会社赤星産業</t>
+          <t>日野陸運有限会社</t>
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>大分県大分市竹矢1381-1</t>
+          <t>大分県大分市弁天3丁目1994-54</t>
         </is>
       </c>
       <c r="E152" t="inlineStr"/>
@@ -4019,263 +3891,247 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>赤帽大分県軽自動車運送協同組合</t>
+          <t>トキワ運輸株式会社</t>
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>http://oita.akabou.jp/</t>
+          <t>https://tokiwa.jbplt.jp/</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>大分県大分市花園1丁目7−76</t>
+          <t>大分県大分市徳島3丁目1-15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>097-546-2030</t>
+          <t>097-521-3232</t>
         </is>
       </c>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://oita.akabou.jp/contact/</t>
-        </is>
-      </c>
+      <c r="G153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>大分県農業協同組合</t>
+          <t>イトウライナー株式会社</t>
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>https://priere-oita.com/</t>
+          <t>https://itoliner.com/</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>大分県大分市花園3丁目2番10号</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr"/>
+          <t>大分県大分市新川町1丁目11-15-209</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>0120-939-208</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>株式会社ケイエスエスジー</t>
+          <t>株式会社TRANSPORT稔</t>
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
       <c r="C155" t="inlineStr">
         <is>
-          <t>http://www.kssg.co.jp/index.html</t>
+          <t>https://tp-zin.com/</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>大分県大分市萩原1-12-15</t>
+          <t>大分県大分市新栄町9番7-2号</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>097-552-5941</t>
+          <t>097-579-6711</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>http://www.kssg.co.jp/contact.html</t>
+          <t>https://tp-zin.com/toi.php</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>株式会社ヤクシン運輸</t>
+          <t>サンパワーシステム株式会社</t>
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>http://yakushin-unyu.com/</t>
-        </is>
-      </c>
+      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
-          <t>大分県大分市西大道1丁目1-17</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>097-547-8088</t>
-        </is>
-      </c>
+          <t>大分県大分市東鶴崎3丁目2番10号</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>株式会社風之荘</t>
+          <t>有限会社慎運輸</t>
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>https://yakushin.co.jp/kazenosyo/</t>
-        </is>
-      </c>
+      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
-          <t>大分県大分市西大道町1丁目1-17</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>097-544-4444</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/yakushing</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://yakushin.co.jp/kazenosyo/contact/</t>
-        </is>
-      </c>
+          <t>大分県大分市横尾東町4丁目13番21号</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>株式会社大分サービス</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr"/>
+          <t>日本貨物株式会社</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>info@nihonkamotsu.co.jp</t>
+        </is>
+      </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>https://www.oita-service.com/info.html</t>
+          <t>https://www.nihonkamotsu.co.jp/</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>大分県大分市西新地1丁目32-1</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>097-551-9150</t>
-        </is>
-      </c>
+          <t>大分県大分市牧1645-1</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.nihonkamotsu.co.jp/contact.html</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>株式会社薬秀</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr"/>
+          <t>赤帽大分運送</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>akabouoita@air.ocn.ne.jp</t>
+        </is>
+      </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>https://yakuhide.co.jp/</t>
+          <t>https://www.oita-akabou.com/</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>大分県大分市豊海1-3-2</t>
+          <t>大分県大分市生石40−4</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>097-537-1111</t>
+          <t>0120-606-601</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://yakuhide.co.jp/contact/</t>
+          <t>https://www.oita-akabou.com</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>株式会社大分宇部</t>
+          <t>住吉運輸産業株式会社</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="inlineStr">
         <is>
-          <t>https://www.nxcl.co.jp/</t>
+          <t>https://www.seagatecorp.com/company/associated/</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>大分県大分市豊海1-7-4</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr"/>
+          <t>大分県大分市生石5-3-1</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>097-534-3741</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.nxcl.co.jp/contact/</t>
+          <t>https://www.seagatecorp.com/contact/</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>豊岡興産有限会社</t>
+          <t>野津運送株式会社</t>
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="inlineStr">
         <is>
-          <t>https://tsukulink.net/oita/city_442011/676179</t>
+          <t>https://notsu.jp/</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>大分県大分市豊海2-199-209清新産業内</t>
+          <t>大分県大分市畑中3丁目3番76号</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>097-536-1087</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/tsukulink</t>
-        </is>
-      </c>
+          <t>097-545-3623</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://tsukulink.net/contacts</t>
+          <t>https://notsu.jp/toiawase/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>有限会社渡辺重機</t>
+          <t>有限会社赤星産業</t>
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr">
         <is>
-          <t>大分県大分市豊海2丁目1994-209</t>
+          <t>大分県大分市竹矢1381-1</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -4285,81 +4141,81 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>大分物流サービス株式会社</t>
+          <t>赤帽大分県軽自動車運送協同組合</t>
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="inlineStr">
         <is>
-          <t>http://ooita-b.co.jp/</t>
+          <t>http://oita.akabou.jp/</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>大分県大分市豊海3丁目1994-192</t>
+          <t>大分県大分市花園1丁目7−76</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>097-533-8062</t>
+          <t>097-546-2030</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr">
         <is>
-          <t>http://ooita-b.co.jp/inquiry/</t>
+          <t>https://oita.akabou.jp/contact/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>大成倉庫株式会社</t>
+          <t>株式会社ケイエスエスジー</t>
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="inlineStr">
         <is>
-          <t>https://www.taiseisoko.co.jp/</t>
+          <t>http://www.kssg.co.jp/index.html</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>大分県大分市豊海4-2-1</t>
+          <t>大分県大分市萩原1-12-15</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>097-533-1118</t>
+          <t>097-552-5941</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.taiseisoko.co.jp/contact</t>
+          <t>http://www.kssg.co.jp/contact.html</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>九州バイパス運輸株式会社</t>
+          <t>株式会社ヤクシン運輸</t>
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="inlineStr">
         <is>
-          <t>https://www.klb-oita.com/relatedcompany1.html</t>
+          <t>http://yakushin-unyu.com/</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>大分県大分市豊海5-3-3</t>
+          <t>大分県大分市西大道1丁目1-17</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>097-537-3738</t>
+          <t>097-547-8088</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
@@ -4368,151 +4224,147 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>株式会社共同運輸</t>
+          <t>株式会社薬秀</t>
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="inlineStr">
         <is>
-          <t>https://miura-gr.com/</t>
+          <t>https://yakuhide.co.jp/</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>大分県大分市豊海5丁目4−9</t>
+          <t>大分県大分市豊海1-3-2</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>097-547-8001</t>
+          <t>097-537-1111</t>
         </is>
       </c>
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://miura-gr.com/%e3%81%8a%e5%95%8f%e3%81%84%e5%90%88%e3%82%8f%e3%81%9b/</t>
+          <t>https://yakuhide.co.jp/contact/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>エム・ケイ運輸有限会社</t>
+          <t>豊岡興産有限会社</t>
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="inlineStr"/>
       <c r="D167" t="inlineStr">
         <is>
-          <t>大分県大分市迫966番地</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr"/>
+          <t>大分県大分市豊海2-199-209清新産業内</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>097-536-1087</t>
+        </is>
+      </c>
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>株式会社エコ・テックエダマ</t>
+          <t>大分物流サービス株式会社</t>
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
       <c r="C168" t="inlineStr">
         <is>
-          <t>https://eco-tech-edama.jp/</t>
+          <t>http://ooita-b.co.jp/</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>大分県大分市都町4丁目3-26都町コーポ201</t>
+          <t>大分県大分市豊海3丁目1994-192</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>097-532-1886</t>
+          <t>097-533-8062</t>
         </is>
       </c>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://eco-tech-edama.jp/pages/5/</t>
+          <t>http://ooita-b.co.jp/inquiry/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>大分運輸株式会社</t>
+          <t>大成倉庫株式会社</t>
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
       <c r="C169" t="inlineStr">
         <is>
-          <t>https://oitaunyu.jbplt.jp/</t>
+          <t>https://www.taiseisoko.co.jp/</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>大分県大分市金池町2丁目11番1号</t>
+          <t>大分県大分市豊海4-2-1</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>097-532-2338</t>
+          <t>097-533-1118</t>
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.taiseisoko.co.jp/contact</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>株式会社幸葬儀社</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>info@yukisougi.com</t>
-        </is>
-      </c>
+          <t>九州バイパス運輸株式会社</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
       <c r="C170" t="inlineStr">
         <is>
-          <t>https://www.yukisougi.com/</t>
+          <t>https://www.klb-oita.com/relatedcompany1.html</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>大分県大分市長浜1-7-8</t>
+          <t>大分県大分市豊海5-3-3</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>097-532-4531</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/yukisougisya</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.yukisougi.com/inquiry/</t>
-        </is>
-      </c>
+          <t>097-537-3738</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>新豊商事有限会社</t>
+          <t>エム・ケイ運輸有限会社</t>
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
-          <t>大分県大分市長浜町3-4-2</t>
+          <t>大分県大分市迫966番地</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -4522,347 +4374,339 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>株式会社オー・エム・ケイ</t>
+          <t>株式会社エコ・テックエダマ</t>
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="inlineStr">
         <is>
-          <t>https://www.daimatsu.jp/%e4%bc%9a%e7%a4%be%e6%a6%82%e8%a6%81/</t>
+          <t>https://eco-tech-edama.jp/</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>大分県大分市青崎1丁目10-5</t>
+          <t>大分県大分市都町4丁目3-26都町コーポ201</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>097-522-2244</t>
+          <t>097-532-1886</t>
         </is>
       </c>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://eco-tech-edama.jp/pages/5/</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>株式会社コープサービスおおいた</t>
+          <t>大分運輸株式会社</t>
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="inlineStr">
         <is>
-          <t>https://www.coopserviceoita.com/</t>
+          <t>https://oitaunyu.jbplt.jp/</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>大分県大分市青崎1丁目9番35号</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr"/>
+          <t>大分県大分市金池町2丁目11番1号</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>097-532-2338</t>
+        </is>
+      </c>
       <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.coopserviceoita.com/mailfoam/</t>
-        </is>
-      </c>
+      <c r="G173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>YOU Corporation株式会社</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>MAIL.you_co_ltd@yahoo.co.jp</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>https://www.you-corp.co.jp/</t>
-        </is>
-      </c>
+          <t>新豊商事有限会社</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr"/>
       <c r="D174" t="inlineStr">
         <is>
-          <t>大分県大分市青崎2丁目132番地</t>
+          <t>大分県大分市長浜町3-4-2</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>097-574-4577</t>
+          <t>097-532-4949</t>
         </is>
       </c>
       <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.you-corp.co.jp/#k07</t>
-        </is>
-      </c>
+      <c r="G174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>有限会社東京運送</t>
+          <t>株式会社コープサービスおおいた</t>
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
       <c r="C175" t="inlineStr">
         <is>
-          <t>https://shinsei-g.avai-lab.com/tokyo-unso/corp_info.php</t>
+          <t>https://www.coopserviceoita.com/</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>大分県大分市須賀1丁目8-4</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>097-521-4092</t>
-        </is>
-      </c>
+          <t>大分県大分市青崎1丁目9番35号</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
       <c r="F175" t="inlineStr"/>
-      <c r="G175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.coopserviceoita.com/mailfoam/</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>竜伸建設工業株式会社</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr"/>
+          <t>YOU Corporation株式会社</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>MAIL.you_co_ltd@yahoo.co.jp</t>
+        </is>
+      </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>https://ryushinkk.com/</t>
+          <t>https://www.you-corp.co.jp/</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>大分県大分市須賀2丁目5番38号</t>
+          <t>大分県大分市青崎2丁目132番地</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>097-578-7808</t>
+          <t>097-574-4577</t>
         </is>
       </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://ryushinkk.com/contact</t>
+          <t>https://www.you-corp.co.jp/#k07</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>株式会社AE物流</t>
+          <t>有限会社東京運送</t>
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="inlineStr">
         <is>
-          <t>http://www.ae-logi.com/</t>
+          <t>https://shinsei-g.avai-lab.com/tokyo-unso/corp_info.php</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>大分県大分市高松1丁目7−36 サンシャイン高城 1F</t>
+          <t>大分県大分市須賀1丁目8-4</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>096-201-1246</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/aebuturyu20180418</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.ae-logi.com/contact</t>
-        </is>
-      </c>
+          <t>097-521-4092</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>株式会社AEトランスポート</t>
+          <t>株式会社AE物流</t>
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
       <c r="C178" t="inlineStr">
         <is>
-          <t>http://ae-transport.jp/</t>
+          <t>http://www.ae-logi.com/</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>大分県大分市高松1丁目7−番36号 サンシャイン高城103</t>
+          <t>大分県大分市高松1丁目7−36 サンシャイン高城 1F</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>097-504-1801</t>
+          <t>096-201-1246</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/aetransport.inc</t>
+          <t>https://www.instagram.com/aebuturyu20180418</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://ae-transport.jp/contact</t>
+          <t>https://www.ae-logi.com/contact</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>株式会社一吉工業</t>
+          <t>株式会社AEトランスポート</t>
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="inlineStr">
         <is>
-          <t>https://144.co.jp/</t>
+          <t>http://ae-transport.jp/</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>大分県大分市高松1丁目9番15号</t>
+          <t>大分県大分市高松1丁目7−番36号 サンシャイン高城103</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>097-594-0144</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr"/>
+          <t>097-504-1801</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/aetransport.inc</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://144.co.jp/%e3%81%8a%e5%95%8f%e3%81%84%e5%90%88%e3%82%8f%e3%81%9b/</t>
+          <t>https://ae-transport.jp/contact</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>中川物流サービス株式会社</t>
+          <t>株式会社一吉工業</t>
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
-      <c r="C180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://144.co.jp/</t>
+        </is>
+      </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>大分県大分市高松東2-3-18</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr"/>
+          <t>大分県大分市高松1丁目9番15号</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>097-594-0144</t>
+        </is>
+      </c>
       <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://144.co.jp/%e3%81%8a%e5%95%8f%e3%81%84%e5%90%88%e3%82%8f%e3%81%9b/</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>明日葉運送</t>
+          <t>中川物流サービス株式会社</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
-          <t>大分県大分市鬼崎576</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr"/>
+          <t>大分県大分市高松東2-3-18</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>097-552-3111</t>
+        </is>
+      </c>
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>株式会社東九運輸</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>info-tokyu@takasui.co.jp</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>https://tokyu-transport.com/</t>
-        </is>
-      </c>
+          <t>明日葉運送</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr"/>
       <c r="D182" t="inlineStr">
         <is>
-          <t>大分県宇佐市北宇佐1619</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>0978-37-0373</t>
-        </is>
-      </c>
+          <t>大分県大分市鬼崎576</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr"/>
       <c r="G182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>株式会社知裕運輸</t>
+          <t>下原商事株式会社</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>https://www.chihirounyu.com/</t>
-        </is>
-      </c>
+      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
-          <t>大分県宇佐市富山1177</t>
+          <t>大分県宇佐市大字北宇佐252番地の4</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>0978-25-9990</t>
+          <t>0978-37-3337</t>
         </is>
       </c>
       <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.chihirounyu.com/contact.php</t>
-        </is>
-      </c>
+      <c r="G183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>株式会社NSUトランスポート</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr"/>
+          <t>株式会社東九運輸</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>info-tokyu@takasui.co.jp</t>
+        </is>
+      </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>http://nsu-transport.trapack.jp/</t>
+          <t>https://tokyu-transport.com/</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>大分県宇佐市富山507−1</t>
+          <t>大分県宇佐市大字北宇佐字前田1619-1</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>0978-25-8101</t>
+          <t>0978-37-0373</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -4871,77 +4715,73 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>有限会社城松運輸</t>
+          <t>合同会社令和</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>https://joushouunyu.com/</t>
-        </is>
-      </c>
+      <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr">
         <is>
-          <t>大分県宇佐市浜高家165−1</t>
+          <t>大分県宇佐市大字四日市903番地</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>0978-25-7200</t>
+          <t>0978-27-8137</t>
         </is>
       </c>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://joushouunyu.com/contact/</t>
-        </is>
-      </c>
+      <c r="G185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>有限会社辻田運輸</t>
+          <t>株式会社知裕運輸</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
       <c r="C186" t="inlineStr">
         <is>
-          <t>https://tsujita-group.com/greetings/tsujita_unyu/</t>
+          <t>https://www.chihirounyu.com/</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>大分県宇佐市猿渡糸口山1120−30</t>
+          <t>大分県宇佐市大字富山1099番地の1</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>0978-33-1122</t>
+          <t>0978-25-9990</t>
         </is>
       </c>
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://tsujita-group.com/contact/</t>
+          <t>https://www.chihirounyu.com/contact.php</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>親和流通株式会社</t>
+          <t>株式会社NSUトランスポート</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
-      <c r="C187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>http://nsu-transport.trapack.jp/</t>
+        </is>
+      </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>大分県宇佐市芝原5−1</t>
+          <t>大分県宇佐市大字富山507番地の1</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>0978-33-1311</t>
+          <t>0978-25-8101</t>
         </is>
       </c>
       <c r="F187" t="inlineStr"/>
@@ -4950,90 +4790,90 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>株式会社真.運送</t>
+          <t>株式会社NSU物流サービス</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="inlineStr">
         <is>
-          <t>http://makotounsou.com/</t>
+          <t>http://www.nsu-group.co.jp/</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>大分県宇佐市長洲3957−1</t>
+          <t>大分県宇佐市大字富山507番地の1</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>0978-38-0576</t>
+          <t>0978-32-1000</t>
         </is>
       </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.makotounsou.com/contact</t>
+          <t>https://nsu-group.co.jp/contact/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>三浦運送株式会社</t>
+          <t>株式会社NSUロード・ライン</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
-          <t>大分県日田市三和991−2</t>
-        </is>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>0973-24-2823</t>
-        </is>
-      </c>
+          <t>大分県宇佐市大字富山507番地の2</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
       <c r="G189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>アストラ物流株式会社</t>
+          <t>有限会社豊栄運輸</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>大分県日田市北豆田1495−3</t>
-        </is>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>0973-28-6464</t>
-        </is>
-      </c>
+          <t>大分県宇佐市大字山袋244</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
       <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>有限会社玉川運輸</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
+          <t>株式会社アクト物流</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>info@act-group.jp</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>https://www.act-group.jp/butsuryu/index.html</t>
+        </is>
+      </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>大分県日田市十二町 玉川町64-15</t>
+          <t>大分県宇佐市大字日足字伏田988-1</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>0973-22-3780</t>
+          <t>0978-34-2077</t>
         </is>
       </c>
       <c r="F191" t="inlineStr"/>
@@ -5042,19 +4882,19 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>日田運送有限会社</t>
+          <t>親和流通株式会社</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr">
         <is>
-          <t>大分県日田市高瀬7977−1</t>
+          <t>大分県宇佐市大字芝原5-1</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>0973-24-3167</t>
+          <t>0978-33-1311</t>
         </is>
       </c>
       <c r="F192" t="inlineStr"/>
@@ -5063,260 +4903,248 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>大分高速運輸有限会社</t>
+          <t>有限会社大翔陸運</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="inlineStr">
         <is>
-          <t>https://www.e-nakayama.co.jp/pages/40/</t>
+          <t>https://oita.tellogs.com/i3036552</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>大分県杵築市中642</t>
+          <t>大分県宇佐市大字西大堀字立山16-1</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>0978-63-5852</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/nakayamaunyu3415</t>
-        </is>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>https://www.e-nakayama.co.jp/pages/3/b_id=7/r_id=1/#block7-1</t>
-        </is>
-      </c>
+          <t>0978-38-7030</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>豊後通運株式会社</t>
+          <t>株式会社トランスキャリー</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="inlineStr">
         <is>
-          <t>https://www.bungo-tsuun.co.jp/company/sales-office/</t>
+          <t>https://transcarry.jp/</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>大分県杵築市大字溝井1484番地20</t>
+          <t>大分県宇佐市大字赤尾852番地</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>0978-62-2320</t>
+          <t>0978-25-8230</t>
         </is>
       </c>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.bungo-tsuun.co.jp/contact/</t>
+          <t>https://transcarry.jp/publics/index/5/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>株式会社九州錦運輸</t>
+          <t>株式会社真・運送</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="inlineStr">
         <is>
-          <t>http://www.nishiki-net.co.jp/</t>
+          <t>https://www.makotounsou.com/company</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>大分県杵築市日野1741</t>
-        </is>
-      </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>0978-62-5521</t>
-        </is>
-      </c>
+          <t>大分県宇佐市大字長洲3957-1</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr">
         <is>
-          <t>http://www.nishiki-net.co.jp/inquiry.html</t>
+          <t>https://www.makotounsou.com/contact</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>龍南運送株式会社</t>
+          <t>有限会社城松運輸</t>
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="inlineStr">
         <is>
-          <t>http://www.ryunan.com/</t>
+          <t>https://joushouunyu.com/</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>大分県津久見市大字下青江3891番地</t>
+          <t>大分県宇佐市浜高家165-1</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>0972-82-5281</t>
+          <t>0978-25-7200</t>
         </is>
       </c>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr">
         <is>
-          <t>http://www.ryunan.com/contact/</t>
+          <t>https://joushouunyu.com/contact/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>武田建材運輸有限会社</t>
+          <t>有限会社辻田運輸</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
-      <c r="C197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>https://tsujita-group.com/greetings/tsujita_unyu/</t>
+        </is>
+      </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>大分県玖珠郡九重町右田1955−19</t>
+          <t>大分県宇佐市猿渡1120-30</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>0973-76-3114</t>
+          <t>0978-33-1122</t>
         </is>
       </c>
       <c r="F197" t="inlineStr"/>
-      <c r="G197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://tsujita-group.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>有限会社玖珠運送</t>
+          <t>有限会社長洲急配</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>http://www.kusutra.co.jp/</t>
-        </is>
-      </c>
+      <c r="C198" t="inlineStr"/>
       <c r="D198" t="inlineStr">
         <is>
-          <t>大分県玖珠郡九重町右田2006−3</t>
-        </is>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>0973-73-3003</t>
-        </is>
-      </c>
+          <t>大分県宇佐市貴船町1-9</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>http://www.kusutra.co.jp/contact</t>
-        </is>
-      </c>
+      <c r="G198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>九重運輸有限会社</t>
+          <t>株式会社真.運送</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>https://r.goope.jp/kokonoe-unyu/</t>
+          <t>http://makotounsou.com/</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>大分県玖珠郡九重町引治493−1</t>
+          <t>大分県宇佐市長洲3957−1</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>0973-78-8820</t>
+          <t>0978-38-0576</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://r.goope.jp/kokonoe-unyu/contact</t>
+          <t>https://www.makotounsou.com/contact</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>株式会社しのはら運送</t>
+          <t>株式会社セイワ</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>https://usa-sjcp.com/?p=1852</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>大分県玖珠郡九重町田野996−1</t>
+          <t>大分県宇佐市院内町香下872-2</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>0973-79-3321</t>
+          <t>0978-42-7388</t>
         </is>
       </c>
       <c r="F200" t="inlineStr"/>
-      <c r="G200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://usa-sjcp.com/?page_id=2612</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>新和軽運社</t>
+          <t>有限会社吉瀬</t>
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
-          <t>大分県玖珠郡玖珠町塚脇562−3−12</t>
-        </is>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>0973-77-2710</t>
-        </is>
-      </c>
+          <t>大分県日田市三本松1-12-8</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>連協運送有限会社</t>
+          <t>アストラ物流株式会社</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
-          <t>大分県玖珠郡玖珠町大隈311−1</t>
+          <t>大分県日田市北豆田1495−3</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>0973-72-6121</t>
+          <t>0973-28-6464</t>
         </is>
       </c>
       <c r="F202" t="inlineStr"/>
@@ -5325,73 +5153,53 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>大分県玖珠運輸事業協同組合</t>
+          <t>有限会社森山運送</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
-          <t>大分県玖珠郡玖珠町山田181</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>0973-72-5737</t>
-        </is>
-      </c>
+          <t>大分県日田市南元町11-38</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>株式会社魚返産業運輸</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>osu@ogaeri.com</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>https://ogaeri.com/</t>
-        </is>
-      </c>
+          <t>丸亀運送株式会社</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr"/>
+      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
-          <t>大分県玖珠郡玖珠町山田2730−1</t>
-        </is>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>0973-72-9033</t>
-        </is>
-      </c>
+          <t>大分県日田市大字三和2689-1</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr"/>
       <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://ogaeri.com/%e3%81%8a%e5%95%8f%e3%81%84%e5%90%88%e3%82%8f%e3%81%9b/</t>
-        </is>
-      </c>
+      <c r="G204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>合谷運輸有限会社</t>
+          <t>三浦運送株式会社</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr">
         <is>
-          <t>大分県玖珠郡玖珠町岩室36−1</t>
+          <t>大分県日田市大字三和991-2</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>0973-72-0076</t>
+          <t>0973-24-2823</t>
         </is>
       </c>
       <c r="F205" t="inlineStr"/>
@@ -5400,263 +5208,207 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>株式会社寛屋陸運</t>
+          <t>KTフォレスト株式会社</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
-      <c r="C206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>https://kyuuei-recruit.com/ktforest/</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>大分県玖珠郡玖珠町戸畑644</t>
+          <t>大分県日田市大字三和字長渕2603-1</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>0973-73-8161</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr"/>
-      <c r="G206" t="inlineStr"/>
+          <t>0973-29-8877</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kyuuei_transport.co.ltd</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://kyuuei-recruit.com/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>株式会社挾間物流サービス</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>k.sumi@hasama-butsuryu.co.jp</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>https://hasama-logistics.jp/</t>
-        </is>
-      </c>
+          <t>株式会社トラストライン</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr">
         <is>
-          <t>大分県由布市庄内町大龍1255−33</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>097-582-2288</t>
-        </is>
-      </c>
+          <t>大分県日田市大字内河野642番地2</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://hasama-logistics.jp/contact</t>
-        </is>
-      </c>
+      <c r="G207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>株式会社城東運輸</t>
+          <t>梶原興業運輸株式会社</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>http://www.joutou-unyu.com/company.html</t>
-        </is>
-      </c>
+      <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr">
         <is>
-          <t>大分県由布市挾間町来鉢189番地1</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>097-583-3300</t>
-        </is>
-      </c>
+          <t>大分県日田市大字北豆田1284</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>http://www.joutou-unyu.com/otoiawase.html</t>
-        </is>
-      </c>
+      <c r="G208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>有限会社荻運送</t>
+          <t>有限会社天本興業</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr"/>
       <c r="D209" t="inlineStr">
         <is>
-          <t>大分県竹田市荻町馬場412−1</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>0974-68-3010</t>
-        </is>
-      </c>
+          <t>大分県日田市大字十二町134-1</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr"/>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>有限会社藤義運輸</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr"/>
+          <t>日田中央木材運輸有限会社</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>info@hita-chumoku.jp</t>
+        </is>
+      </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>https://fujiyoshi-transport.com/</t>
+          <t>http://hita-chumoku.jp/company</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>大分県竹田市荻町高練木2335−4</t>
+          <t>大分県日田市大字友田2468-3</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>0974-68-2771</t>
+          <t>0973-22-5117</t>
         </is>
       </c>
       <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>http://hita-chumoku.jp/contact/</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>有限会社藤野屋運送</t>
+          <t>光岡輸送有限会社</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>https://www.fujinoyaweb.co.jp/company</t>
+          <t>http://www.kawanami-web.com/html/yusou/yusou.htm</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>大分県竹田市菅生943−1</t>
+          <t>大分県日田市大字友田3725</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>0974-65-2345</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/fujinoyaweb</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.fujinoyaweb.co.jp/contact/</t>
-        </is>
-      </c>
+          <t>0973-22-6145</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>有限会社福伸急送</t>
+          <t>山ア運送株式会社</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>https://fukushinkyuso.com/</t>
-        </is>
-      </c>
+      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
-          <t>大分県臼杵市大字江無田1524番地の1</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>0978-63-2250</t>
-        </is>
-      </c>
+          <t>大分県日田市大字友田80-2</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr"/>
       <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://fukushinkyuso.com/contact/</t>
-        </is>
-      </c>
+      <c r="G212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>有限会社トランスポートサービス・ミエノ</t>
+          <t>有限会社セイコー運輸</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>http://ts-mieno.com/</t>
-        </is>
-      </c>
+      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
-          <t>大分県臼杵市大字稲田1000−1</t>
-        </is>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>0972-63-6696</t>
-        </is>
-      </c>
+          <t>大分県日田市大字小迫字鳥越32-1-2</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr"/>
       <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://ts-mieno.com/contact/</t>
-        </is>
-      </c>
+      <c r="G213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>株式会社KDS</t>
+          <t>株式会社髙松クレーン運輸</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>https://www.kds-0024.com/</t>
-        </is>
-      </c>
+      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
-          <t>大分県豊後大野市三重町内田3617番地1</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>0974-22-0970</t>
-        </is>
-      </c>
+          <t>大分県日田市大字日高546番地4</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr"/>
       <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://www.kds-0024.com/contact</t>
-        </is>
-      </c>
+      <c r="G214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>株式会社ユタカ産業運輸</t>
+          <t>有限会社博井商店</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
-          <t>大分県豊後大野市千歳町長峰字桑迫1590番地</t>
+          <t>大分県日田市大字有田1720-1</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -5666,48 +5418,1901 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>高田通運株式会社</t>
+          <t>株式会社下徳産業</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>https://www.hotnavi-bt.jp/company/detail/?id=201404111722464305</t>
-        </is>
-      </c>
+      <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>大分県豊後高田市新栄1379番地6</t>
-        </is>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>0978-22-2485</t>
-        </is>
-      </c>
+          <t>大分県日田市大字有田319-12</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr"/>
       <c r="F216" t="inlineStr"/>
       <c r="G216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>株式会社近藤運送</t>
+          <t>株式会社U-PLUS</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr"/>
       <c r="D217" t="inlineStr">
         <is>
-          <t>大分県豊後高田市草地3255</t>
-        </is>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>0978-22-3295</t>
-        </is>
-      </c>
+          <t>大分県日田市大字東有田2579-15</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr"/>
       <c r="F217" t="inlineStr"/>
       <c r="G217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>有限会社トランスポートサービス・カワヅ</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr"/>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>大分県日田市大字渡里636-1</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>山森運送</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr"/>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>大分県日田市大字石井1126-3</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>0973-22-7047</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>有限会社タカシマ運送</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr"/>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>大分県日田市大字石井289-6</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>キャリー有限会社</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr"/>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>大分県日田市大字石井777番地</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>株式会社三配</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr"/>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>大分県日田市大字花月1077番地1</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>株式会社合谷産業運輸</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr"/>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>大分県日田市大字高井町129-1</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>有限会社コウチョウ運輸</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr"/>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>大分県日田市大字高瀬2296-7</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>日田運送有限会社</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr"/>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>大分県日田市大字高瀬7977-1</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>0973-24-3167</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>有限会社髙森</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>大分県日田市大山町西大山395-10</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>郡森運送有限会社</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr"/>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>大分県日田市天瀬町五馬市300番地</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>株式会社大征産業</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>大分県日田市天瀬町塚田1443番地</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>0973-57-3303</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>株式会社TOMODA</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>大分県日田市天瀬町女子畑944番地3</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>株式会社アサヒサービス</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>大分県日田市玉川町 3-649-4</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>有限会社玉川運輸</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr"/>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>大分県日田市玉川町64</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>0973-22-3780</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>日田陸運株式会社</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr"/>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>大分県日田市石井町1-272-1</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>大分高速運輸有限会社</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr"/>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://www.e-nakayama.co.jp/pages/40/</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>大分県杵築市大字中642</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>0978-63-5852</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nakayamaunyu3415</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.e-nakayama.co.jp/pages/3/b_id=7/r_id=1/#block7-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>有限会社ハウスフジワラ</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr"/>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>大分県杵築市大字大内4093番地</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>有限会社日野産業運輸</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr"/>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>大分県杵築市大字大内980-43</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>0978-63-6988</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>豊後通運株式会社</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://www.bungo-tsuun.co.jp/</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>大分県杵築市大字溝井1484番地20</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>0978-62-2320</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://www.bungo-tsuun.co.jp/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>国東運輸株式会社</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr"/>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>http://www.kunisaki-y.co.jp/index.html</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>大分県杵築市大字狩宿2509-30</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>0978-63-8800</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>株式会社九州錦運輸</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr"/>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>http://www.nishiki-net.co.jp/</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>大分県杵築市大字猪尾781-1</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>0978-62-5521</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>http://www.nishiki-net.co.jp/inquiry.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>たちばな運輸株式会社</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr"/>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>大分県津久見市上青江3370-8</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>龍南運送株式会社</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr"/>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>http://www.ryunan.com/</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>大分県津久見市下青江3891</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>097-532-1713</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>http://www.ryunan.com/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>有限会社新五運送</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>大分県津久見市大字下青江3631-6</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>有限会社協和産業</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr"/>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>http://e-kyowa.com/</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>大分県津久見市大字津久見1453-1</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>0972-82-3661</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kyowa_industry</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>武田建材運輸有限会社</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr"/>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡九重町大字右田1955-19</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>0973-76-3114</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>有限会社玖珠運送</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr"/>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>http://www.kusutra.co.jp/</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡九重町大字右田2006-3</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>0973-73-3003</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>http://www.kusutra.co.jp/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>九重運輸有限会社</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr"/>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>https://r.goope.jp/kokonoe-unyu/</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡九重町大字引治493-1</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>0973-78-8820</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://r.goope.jp/kokonoe-unyu/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>有限会社若竹実業</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡九重町大字田野1393の1</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>0973-79-2363</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>株式会社しのはら運送</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡九重町大字田野996-1</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>0973-79-3321</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>株式会社広栄</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡九重町野上548-3</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>新和軽運社</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr"/>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町塚脇562−3−12</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>0973-77-2710</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>有限会社広成産業</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr"/>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町大字大隈1006番地の2</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>連協運送有限会社</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr"/>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>https://www.big-advance.site/c/207/1460/profile</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町大字大隈311-1</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>0973-72-6121</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://www.big-advance.site/c/207/1460/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>株式会社魚返産業運輸</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>osu@ogaeri.com</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>https://ogaeri.com/</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町大字山田2730-1</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>0973-72-9033</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://ogaeri.com/%e3%81%8a%e5%95%8f%e3%81%84%e5%90%88%e3%82%8f%e3%81%9b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>東久大通運株式会社</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>hkt@e-hkt.com</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>https://higashikyuudai.jimdosite.com/</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町大字山田87-1</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>0973-72-1160</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://higashikyuudai.jimdosite.com/%E3%81%8A%E5%95%8F%E5%90%88%E3%81%9B%E3%80%81%E6%B1%82%E4%BA%BA%E6%83%85%E5%A0%B1/</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>合谷運輸有限会社</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町大字帆足450-1</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>0973-72-0076</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>株式会社寛屋陸運</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr"/>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町大字戸畑644番地</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>0973-73-8161</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>有限会社益永中野産業</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr"/>
+      <c r="C256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町大字戸畑7810番地</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>有限会社麻生商店</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町大隈塔の元307-6</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>大分県玖珠運輸事業協同組合</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>大分県玖珠郡玖珠町山田181</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>0973-72-5737</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>クロレラ輸送有限会社</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr"/>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>大分県由布市庄内町大龍2621番地1</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>株式会社挾間物流サービス</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>k.sumi@hasama-butsuryu.co.jp</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>https://hasama-logistics.jp/</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>大分県由布市庄内町大龍字海免1255-33</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>097-582-2288</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://hasama-logistics.jp/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>株式会社城東運輸</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>http://www.joutou-unyu.com/company.html</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>大分県由布市挾間町来鉢189-1</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>097-583-3300</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>http://www.joutou-unyu.com/otoiawase.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>有限会社アゼスト</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr"/>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://www.a-zest.site/</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>大分県由布市挾間町高崎字平田949-2</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>097-586-3388</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/azest523</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>株式会社豊友運輸</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr"/>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>https://tomoken.com/pages/31/</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>大分県竹田市大字会々2808-5</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>0974-63-3343</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tomoken.official</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://tomoken.com/pages/5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>株式会社大昌興産</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr"/>
+      <c r="C264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>大分県竹田市大字挾田2541番地</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>0974-63-4369</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>有限会社藤野屋運送</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>https://www.fujinoyaweb.co.jp/company</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>大分県竹田市大字菅生943-1</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>0974-65-2345</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fujinoyaweb</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://www.fujinoyaweb.co.jp/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>有限会社荻運送</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>大分県竹田市荻町馬場412-1</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>0974-68-3010</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>有限会社藤義運輸</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>https://fujiyoshi-transport.com/</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>大分県竹田市荻町高練木2335-4</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>0974-68-2771</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>有限会社大翔実業</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
+      <c r="C268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字大野字原松ヶ平1434</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>東西運輸株式会社</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr"/>
+      <c r="C269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字市浜777-4</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>有限会社中野高速運輸</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr"/>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字末広3410-1</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>開成輸送株式会社</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr"/>
+      <c r="C271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字末広字黒丸161-1</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>株式会社光進</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr"/>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字江無田1584番地の1</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>臼杵運送株式会社</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr"/>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>https://www.usukiunso.co.jp/</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字福良1766-1</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>097-593-1001</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>有限会社トランスポートサービス・ミエノ</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>http://ts-mieno.com/</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字稲田字中尾下1000-1</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>0972-63-6696</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://ts-mieno.com/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>臼津鉱運株式会社</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr"/>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://kooun.jp/</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字稲田字田ノ口2608-1</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>0972-63-1518</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>有限会社山橋運送</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr"/>
+      <c r="C276" t="inlineStr"/>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字臼杵2-75-43</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>0972-62-2587</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>株式会社アスペックス</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>info@aspex-ind.lol-test.com</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://aspex-ind.com/company/</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>大分県臼杵市大字諏訪604番地の41</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>0972-83-5517</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://aspex-ind.com/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>有限会社福伸急送</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr"/>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>https://fukushinkyuso.com/</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>大分県臼杵市江無田1524-1</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>0978-63-2250</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://fukushinkyuso.com/contact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>有限会社臼三貨物配送</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr"/>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>大分県臼杵市野津町大字宮原3814-1</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>有限会社政和運輸</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
+      <c r="C280" t="inlineStr"/>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>大分県臼杵市野津町大字福良木21</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>有限会社日大</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
+      <c r="C281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>大分県臼杵市野津町大字都原3292</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>株式会社KDS</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>https://www.kds-0024.com/company</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市三重町内田3617-1</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>0974-22-0970</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://www.kds-0024.com/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>東九物流システム株式会社</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr"/>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市三重町芦刈481-81</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>東九運送有限会社</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市三重町菅生422番地6</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>株式会社平山運輸</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr"/>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市三重町菅生431番地253</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>有限会社雄翔</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr"/>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://yusho-co.jp/company.html</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市三重町赤嶺1151-6</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>有限会社ヤマサキ</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市千歳町前田1249-3</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>株式会社ユタカ産業運輸</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
+      <c r="C288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市千歳町長峰1590</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>株式会社千歳運送</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr"/>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://n-seikei.jp/2025/08/post-112285.html</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市千歳町長峰267</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>0974-37-2078</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>http://n-seikei.jp/contact.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>ビッグライン株式会社</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>info@tomookagumi.co.jp</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://tomookagumi.co.jp/group/</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市大野町大原1155</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>0974-34-2323</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/tomookagumi</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://tomookagumi.co.jp/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>有限会社工藤産業</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr"/>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市大野町田中126</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>0974-34-2167</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>清川物流株式会社</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr"/>
+      <c r="C292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市清川町砂田1681</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>有限会社竜成運輸</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr"/>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市犬飼町下津尾2039-1</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>097-586-8233</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>犬飼運送有限会社</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr"/>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>大分県豊後大野市犬飼町田原913</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>高田通運株式会社</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr"/>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://www.hotnavi-bt.jp/company/detail/?id=201404111722464305</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>大分県豊後高田市新栄1379-6</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>0978-22-2485</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>株式会社うるしま運輸</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>大分県豊後高田市森485-1</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>株式会社近藤運送</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr"/>
+      <c r="C297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>大分県豊後高田市草地3255-7</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>0978-22-3295</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>有限会社大洋運輸</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>info@taiyoexp.com</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://taiyoexp.com/company/</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>大分県速見郡日出町大字大神1477番地1</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>0972-28-5779</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://taiyoexp.com/contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>日出開発運輸有限会社</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr"/>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>大分県速見郡日出町大字大神8115-1</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>有限会社ダイセン運輸</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>大分県速見郡日出町大字川崎2445-1</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>喜和屋運輸有限会社</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
+      <c r="C301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>大分県速見郡日出町大字川崎字新田838-11</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>株式会社AYUSHOU</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>大分県速見郡日出町大字藤原2352番地</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
